--- a/Current TAPPs/Lab-XCT_TAPP_v37.xlsx
+++ b/Current TAPPs/Lab-XCT_TAPP_v37.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legends" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TAPP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legends" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="4" customWidth="1" min="13" max="13"/>
@@ -609,7 +609,7 @@
           <t>Keyed By</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
@@ -918,7 +918,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="1" t="n"/>
       <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1048,7 +1048,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="1" t="n"/>
       <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1178,7 +1178,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="1" t="n"/>
       <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1308,7 +1308,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="1" t="n"/>
       <c r="K6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1438,7 +1438,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="1" t="n"/>
       <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1568,7 +1568,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="1" t="n"/>
       <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1698,7 +1698,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="1" t="n"/>
       <c r="K9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1828,7 +1828,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="1" t="n"/>
       <c r="K10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1958,7 +1958,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>Encourages formal procedure registration and ensures traceability.</t>
         </is>
@@ -2088,7 +2088,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session, which may cover several samples, and this is the link back to the raw instrument files.</t>
         </is>
@@ -2222,7 +2222,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="1" t="n"/>
       <c r="K13" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2352,7 +2352,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="1" t="n"/>
       <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2482,7 +2482,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="1" t="n"/>
       <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2612,7 +2612,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="1" t="n"/>
       <c r="K16" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2742,7 +2742,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="1" t="n"/>
       <c r="K17" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -2872,7 +2872,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="1" t="n"/>
       <c r="K18" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3002,7 +3002,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>Provides a stable, citable link to the companion method independent of whether a dataset has been deposited.</t>
         </is>
@@ -3136,7 +3136,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="1" t="n"/>
       <c r="K20" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3369,7 +3369,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr">
         <is>
           <t>Used for discoverability and procedure matching, and because the material type constrains sample preparation, calibration and matrix-matching requirements.</t>
         </is>
@@ -3503,7 +3503,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr">
         <is>
           <t>Defines the scientific purpose of the scan and informs resolution and contrast requirements. Used for procedure discoverability: a researcher can identify whether this procedure is suitable for their scientific question.</t>
         </is>
@@ -3633,7 +3633,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr">
         <is>
           <t>Samples spanning fewer than that are difficult to characterize reliably.</t>
         </is>
@@ -3763,7 +3763,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr">
         <is>
           <t>The maximum dimension constrains the minimum achievable field of view and therefore the coarsest achievable voxel size. The minimum dimension determines how many voxels span the smallest feature of interest.</t>
         </is>
@@ -3893,7 +3893,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr">
         <is>
           <t>Particularly important for meteorite, mission-returned, and other restricted samples. The actual sample mass depends on the specific sample being scanned, not on the procedure design.</t>
         </is>
@@ -4023,7 +4023,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="1" t="n"/>
       <c r="K28" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4153,7 +4153,7 @@
           <t>defines: sample</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr">
         <is>
           <t>The analysis record corresponds to one session and may cover several samples.</t>
         </is>
@@ -4287,7 +4287,7 @@
           <t>defines: sampling unit</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
+      <c r="J30" s="1" t="n"/>
       <c r="K30" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4417,7 +4417,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="1" t="n"/>
       <c r="K31" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4543,7 +4543,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr">
         <is>
           <t>XCT is typically non-destructive, with no surface preparation required.</t>
         </is>
@@ -4677,7 +4677,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
+      <c r="J33" s="1" t="n"/>
       <c r="K33" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4807,7 +4807,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="1" t="n"/>
       <c r="K34" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -4933,7 +4933,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
+      <c r="J35" s="1" t="n"/>
       <c r="K35" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5166,7 +5166,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr">
         <is>
           <t>Recording it as a controlled value lets procedures be found by vendor.</t>
         </is>
@@ -5300,7 +5300,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n"/>
+      <c r="J39" s="1" t="n"/>
       <c r="K39" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -5426,7 +5426,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Reflection target configurations are most common in lab XCT (X-rays emitted from the face of the anode toward the sample); transmission target configurations allow smaller focal spots by thinning the anode into a membrane and collecting X-rays from the back, enabling higher spatial resolution at the cost of lower maximum power.</t>
         </is>
@@ -5556,7 +5556,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr">
         <is>
           <t>Determines the characteristic line energies superimposed on the bremsstrahlung continuum, which can affect phase contrast at specific energies. Multi-metal anodes (e.g., W/Mo/Cu) extend the usable energy range.</t>
         </is>
@@ -5686,7 +5686,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr">
         <is>
           <t>Flat-panel detectors (amorphous silicon) are standard in Nikon, NSI, and similar systems. CCD or CMOS detectors coupled to a scintillator via an optical objective are used in Zeiss Xradia Versa systems, enabling optical magnification for sub-micrometre voxel sizes.</t>
         </is>
@@ -5816,7 +5816,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr">
         <is>
           <t>Combined with detector pixel size and geometric magnification, determines the field of view.</t>
         </is>
@@ -5946,7 +5946,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
+      <c r="J44" s="1" t="n"/>
       <c r="K44" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6072,7 +6072,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n"/>
+      <c r="J45" s="1" t="n"/>
       <c r="K45" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6202,7 +6202,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
+      <c r="J46" s="1" t="n"/>
       <c r="K46" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6328,7 +6328,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr">
         <is>
           <t>Often bundled with the instrument and proprietary to the manufacturer.</t>
         </is>
@@ -6462,7 +6462,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="1" t="n"/>
       <c r="K48" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -6695,7 +6695,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="1" t="inlineStr">
         <is>
           <t>Serves as the procedure-level declaration of measurement type, distinct from the mode flag columns, which state per-field applicability. Ensures every procedure record is self-describing and comparable across the library.</t>
         </is>
@@ -6829,7 +6829,7 @@
           <t>defines: reported property</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr">
         <is>
           <t>A procedure may acquire many channels and report a small number of derived quantities; without this field a data consumer cannot tell which.</t>
         </is>
@@ -6959,7 +6959,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="1" t="inlineStr">
         <is>
           <t>Determines the maximum X-ray photon energy and controls penetration depth and phase contrast. Higher voltages provide greater penetration for dense or large samples; lower voltages improve contrast between low-density phases.</t>
         </is>
@@ -7089,7 +7089,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr">
         <is>
           <t>Controls photon flux and therefore projection image SNR. Higher current improves SNR but increases thermal loading on the source and may increase focal spot size.</t>
         </is>
@@ -7219,7 +7219,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr">
         <is>
           <t>Power constrains the achievable focal spot size for microfocal tubes: higher power requires a larger focal spot, trading spatial resolution for SNR. Retained as a standalone field because it is routinely reported in the literature and directly constrains instrument operating limits.</t>
         </is>
@@ -7349,7 +7349,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr">
         <is>
           <t>Hardens the beam by attenuating low-energy photons, reducing beam hardening artifacts and improving CT number stability across the sample.</t>
         </is>
@@ -7479,7 +7479,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr">
         <is>
           <t>Together with SDD, determines geometric magnification (M = SDD/SOD). Shorter SOD increases magnification and reduces voxel size.</t>
         </is>
@@ -7609,7 +7609,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr">
         <is>
           <t>Together with SOD, determines geometric magnification M = SDD/SOD.</t>
         </is>
@@ -7739,7 +7739,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n"/>
+      <c r="J59" s="1" t="n"/>
       <c r="K59" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -7865,7 +7865,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr">
         <is>
           <t>Full 360° rotation is standard for cone-beam lab XCT. 180° rotation (half-scan) is sometimes used for faster acquisition but may introduce additional artifacts.</t>
         </is>
@@ -7995,7 +7995,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr">
         <is>
           <t>More projections improve reconstruction quality by reducing under-sampling streak artifacts but increase scan time.</t>
         </is>
@@ -8125,7 +8125,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr">
         <is>
           <t>Finer step sizes improve angular sampling and reduce streak artifacts at the cost of longer scan time.</t>
         </is>
@@ -8255,7 +8255,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr">
         <is>
           <t>Set as a deliberate choice for the target sample type and voxel size: longer exposures increase SNR at the cost of total scan time.</t>
         </is>
@@ -8385,7 +8385,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="1" t="inlineStr">
         <is>
           <t>Frame averaging reduces random electronic noise.</t>
         </is>
@@ -8515,7 +8515,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="1" t="inlineStr">
         <is>
           <t>Reduces effective resolution while increasing per-pixel SNR and reducing file size.</t>
         </is>
@@ -8645,7 +8645,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="1" t="inlineStr">
         <is>
           <t>Standard practice in all quantitative lab XCT.</t>
         </is>
@@ -8775,7 +8775,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="1" t="inlineStr">
         <is>
           <t>Continuous rotation has been associated with sub-volume rotational mismatch artifacts in multi-volume stitching workflows (Eckley et al. 2025).</t>
         </is>
@@ -8905,7 +8905,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="1" t="inlineStr">
         <is>
           <t>The number of sub-volumes depends on the length of the specific sample being scanned and cannot be fixed in the procedure in advance.</t>
         </is>
@@ -9035,7 +9035,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="1" t="inlineStr">
         <is>
           <t>Eckley et al. (2025) report that 500 slices of overlap were used in the Apollo 73001 stitching workflow, while 180 slices proved insufficient for their cone-beam geometry.</t>
         </is>
@@ -9165,7 +9165,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="1" t="inlineStr">
         <is>
           <t>Useful for assessing beam stability and sample integrity concerns over long scans.</t>
         </is>
@@ -9398,7 +9398,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="1" t="inlineStr">
         <is>
           <t>The Feldkamp-Davis-Kress (FDK) algorithm is standard for cone-beam lab XCT geometry; iterative methods offer better artifact suppression at the cost of computation time.</t>
         </is>
@@ -9528,7 +9528,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="1" t="inlineStr">
         <is>
           <t>Sharper filters (Ram-Lak) enhance edge definition but amplify high-frequency noise; smoother filters (Hann, Hamming) reduce noise at the cost of edge sharpness.</t>
         </is>
@@ -9658,7 +9658,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="1" t="inlineStr">
         <is>
           <t>Beam hardening causes cupping artifacts (CT numbers elevated at sample edges relative to the interior) and can bias segmentation thresholds. Hardware pre-filtering (Group 4: X-ray Pre-filter) and software correction are complementary approaches.</t>
         </is>
@@ -9788,7 +9788,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="1" t="inlineStr">
         <is>
           <t>May be tuned empirically per material type or per scan session.</t>
         </is>
@@ -9918,7 +9918,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="1" t="inlineStr">
         <is>
           <t>Ring artifacts appear as concentric circular bands centred on the rotation axis and arise from defective or miscalibrated detector pixels.</t>
         </is>
@@ -10048,7 +10048,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="1" t="n"/>
       <c r="K78" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10174,7 +10174,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="1" t="inlineStr">
         <is>
           <t>Calibrated CT numbers enable cross-instrument and cross-session comparison and support phase identification by comparison to calculated linear attenuation coefficient (LAC) values (e.g., using MuCalc; Hanna &amp; Ketcham 2017). Uncalibrated grayscale values are instrument- and session-specific.</t>
         </is>
@@ -10304,7 +10304,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>The method must be reported for any quantitative result to be reproducible.</t>
         </is>
@@ -10434,7 +10434,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="1" t="inlineStr">
         <is>
           <t>Documenting these values enables reproducibility assessment and cross-study comparison.</t>
         </is>
@@ -10564,7 +10564,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n"/>
+      <c r="J82" s="1" t="n"/>
       <c r="K82" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10690,7 +10690,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
+      <c r="J83" s="1" t="n"/>
       <c r="K83" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10816,7 +10816,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n"/>
+      <c r="J84" s="1" t="n"/>
       <c r="K84" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -10942,7 +10942,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J85" s="1" t="inlineStr">
         <is>
           <t>Rotational mismatch artifacts have been identified in continuous-rotation acquisitions (~0.35° misalignment in Eckley et al. 2025).</t>
         </is>
@@ -11072,7 +11072,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n"/>
+      <c r="J86" s="1" t="n"/>
       <c r="K86" s="13" t="inlineStr">
         <is>
           <t>N</t>
@@ -11198,7 +11198,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="J87" s="1" t="inlineStr">
         <is>
           <t>Bit depth affects the dynamic range available for phase segmentation and quantitative attenuation analysis.</t>
         </is>
@@ -11328,7 +11328,7 @@
           <t>reported property</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n"/>
+      <c r="J88" s="1" t="n"/>
       <c r="K88" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11458,7 +11458,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n"/>
+      <c r="J89" s="1" t="n"/>
       <c r="K89" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11687,7 +11687,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="J92" s="1" t="inlineStr">
         <is>
           <t>The Nyquist limit sets a theoretical floor at 2× the voxel size.</t>
         </is>
@@ -11817,7 +11817,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="J93" s="1" t="inlineStr">
         <is>
           <t>Beam hardening in polychromatic lab XCT produces a characteristic darker interior and brighter edges in the reconstructed CT number profile, even in compositionally uniform material.</t>
         </is>
@@ -11947,7 +11947,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="J94" s="1" t="inlineStr">
         <is>
           <t>In samples containing linear geological features oriented tangentially to the rotation axis, ring correction can alter or introduce spurious linear features in those orientations.</t>
         </is>
@@ -12077,7 +12077,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="1" t="n"/>
       <c r="K95" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12203,7 +12203,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="J96" s="2" t="inlineStr">
+      <c r="J96" s="1" t="inlineStr">
         <is>
           <t>PVE produces intermediate CT numbers at phase boundaries and at the surfaces of small features, because each voxel integrates the attenuation of all material within its volume. The criterion materially changes reported modal abundances and size distributions, so two datasets are not comparable without it.</t>
         </is>
@@ -12333,7 +12333,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n"/>
+      <c r="J97" s="1" t="n"/>
       <c r="K97" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12459,7 +12459,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J98" s="2" t="inlineStr">
+      <c r="J98" s="1" t="inlineStr">
         <is>
           <t>SNR is controlled by photon flux (source power, exposure time, number of projections) and sample attenuation.</t>
         </is>
@@ -12589,7 +12589,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="J99" s="1" t="inlineStr">
         <is>
           <t>Cross-validation is relevant where CT grey-values alone cannot uniquely distinguish phases with similar attenuation coefficients.</t>
         </is>
@@ -12719,7 +12719,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n"/>
+      <c r="J100" s="1" t="n"/>
       <c r="K100" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12849,7 +12849,7 @@
           <t>(none)</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="1" t="n"/>
       <c r="K101" s="8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12944,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13068,7 +13068,7 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Single-volume</t>
         </is>
       </c>
       <c r="B9" s="1" t="n"/>
@@ -13076,214 +13076,206 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Single-volume</t>
+          <t>Multi-volume stitching</t>
         </is>
       </c>
       <c r="B10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Multi-volume stitching</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n"/>
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>This field applies to this analytical mode and should be reported.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>This field applies to this analytical mode and should be reported.</t>
+          <t>This field does not apply to this analytical mode.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>This field does not apply to this analytical mode.</t>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>What to enter</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Data Type</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>What to enter</t>
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Controlled list</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>Controlled list</t>
+          <t>Controlled list / Text</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Choose one of the values listed in "Example / Allowed Content". The list is CLOSED — it is meant to cover every case. If your value genuinely is not there, that is a gap in the list worth reporting, not a reason to write your own.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>Controlled list / Text</t>
+          <t>Numeric (unit)</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>Numeric (unit)</t>
+          <t>Numeric + unit</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>A number in the unit named in brackets. Enter the number only — the unit is fixed by the field.</t>
+          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>Numeric + unit</t>
+          <t>Text (free)</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>A number AND its unit, because the unit varies between procedures. Write both, e.g. '50 us' or '0.5 s'.</t>
+          <t>Free text. No controlled vocabulary applies.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>Text (free)</t>
+          <t>N/A | None</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>Free text. No controlled vocabulary applies.</t>
+          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>N/A | None</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>Offered by every controlled list. "N/A" means the field does not apply to this procedure; "None" means it applies but nothing was used. Prefer either over leaving the cell blank.</t>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Keyed By (Rule 7)</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>What the field's value repeats over</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Keyed By (Rule 7)</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>What the field's value repeats over</t>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>Scalar — one value per procedure or analysis. The default.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>(none)</t>
+          <t>defines: reported property</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Scalar — one value per procedure or analysis. The default.</t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>defines: reported property</t>
+          <t>defines: sample</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
+          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>defines: sample</t>
+          <t>defines: sampling unit</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. </t>
+          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>defines: sampling unit</t>
+          <t>reported property</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>ENUMERATES the key domain rather than being keyed by it — the header of the child table, not a column in it. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
+          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>reported property</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>One value per reported quantity or nominal property, at any point in the chain — ratios and dates alike, plus their uncertainties.</t>
-        </is>
-      </c>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>Nested — sampling unit exists only within sample. One value per subdivision of the physical sample that carries its own row — grain, spot, aliquot, phase, sub-volume.</t>
         </is>
